--- a/檔案欄位說明.xlsx
+++ b/檔案欄位說明.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\shan\power-bi_advanced-courses\Lung-Cancer-Risk-in-25-Countries_project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\芳珊\202504_Python人工智慧與數據分析\Lung-Cancer-Risk-in-25-Countries_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8CA7EB8-CAE6-4601-B757-3C899FCCECB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64894DD1-152B-49D7-AC2E-1BE9929C4AAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>ID</t>
   </si>
@@ -142,31 +142,42 @@
     <t>醫療可近性，分為：良好/差。</t>
   </si>
   <si>
+    <t>欄位名稱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>欄位說明</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否有早期偵測（是/否）。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>診斷後的癌症期別（第1至第4期，未確診者為 NaN）。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>死亡率（未確診者為 NaN，為浮點數）。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Treatment_Type</t>
+  </si>
+  <si>
+    <t>未治療、化學治療、放射線治療、手術</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>國家層級判定為已開發或開發中國家（是/否）。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>每年肺癌死亡人數（以國家為單位的整數值）。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>肺癌盛行率（以國家為單位的浮點數）。</t>
-  </si>
-  <si>
-    <t>死亡率（未確診者為 NaN，為浮點數）。</t>
-  </si>
-  <si>
-    <t>欄位名稱</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>欄位說明</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否有早期偵測（是/否）。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>診斷後的癌症期別（第1至第4期，未確診者為 NaN）。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -549,22 +560,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B24"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="72.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="72.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -572,7 +583,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -580,7 +591,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -588,7 +599,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
@@ -596,7 +607,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -604,7 +615,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -612,7 +623,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
@@ -620,7 +631,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
@@ -628,7 +639,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -636,7 +647,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -644,7 +655,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -652,15 +663,15 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>12</v>
       </c>
@@ -668,7 +679,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -676,7 +687,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -684,7 +695,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -692,7 +703,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -700,7 +711,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -708,44 +719,52 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
       <c r="B20" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>19</v>
       </c>
-      <c r="B21" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+      <c r="B22" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>20</v>
       </c>
-      <c r="B22" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+      <c r="B23" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>21</v>
       </c>
-      <c r="B23" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+      <c r="B24" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>22</v>
       </c>
-      <c r="B24" t="s">
-        <v>43</v>
+      <c r="B25" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
